--- a/sistema_preenchimento/exports/processados/export_frentes_lmalerbo_2026-05-12.xlsx
+++ b/sistema_preenchimento/exports/processados/export_frentes_lmalerbo_2026-05-12.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L15"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -453,145 +453,145 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>11/05/2026, 22:21:47</v>
+        <v>12/05/2026, 15:23:16</v>
       </c>
       <c r="B2" t="str">
         <v>lmalerbo</v>
       </c>
       <c r="C2">
-        <v>10688001</v>
+        <v>10623001</v>
       </c>
       <c r="D2">
-        <v>10688</v>
+        <v>10623</v>
       </c>
       <c r="E2" t="str">
-        <v>2-M</v>
+        <v>AGROPASTORIL AMERICANA</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-      <c r="H2">
-        <v>26</v>
+      <c r="G2" t="str">
+        <v>—</v>
+      </c>
+      <c r="H2" t="str">
+        <v>—</v>
       </c>
       <c r="I2">
-        <v>16.21</v>
+        <v>6.71</v>
       </c>
       <c r="J2" t="str">
-        <v>SEM LINHAS</v>
+        <v>VANT</v>
       </c>
       <c r="K2" t="str">
-        <v>25-26</v>
+        <v>26-27</v>
       </c>
       <c r="L2" t="str">
-        <v>SEM LINHAS</v>
+        <v>CONCLUIDO</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>11/05/2026, 22:21:47</v>
+        <v>12/05/2026, 15:23:16</v>
       </c>
       <c r="B3" t="str">
         <v>lmalerbo</v>
       </c>
       <c r="C3">
-        <v>10688002</v>
+        <v>10623002</v>
       </c>
       <c r="D3">
-        <v>10688</v>
+        <v>10623</v>
       </c>
       <c r="E3" t="str">
-        <v>2-M</v>
+        <v>AGROPASTORIL AMERICANA</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3">
-        <v>26</v>
+      <c r="G3" t="str">
+        <v>—</v>
+      </c>
+      <c r="H3" t="str">
+        <v>—</v>
       </c>
       <c r="I3">
-        <v>25.29</v>
+        <v>3.61</v>
       </c>
       <c r="J3" t="str">
-        <v>SEM LINHAS</v>
+        <v>VANT</v>
       </c>
       <c r="K3" t="str">
-        <v>25-26</v>
+        <v>26-27</v>
       </c>
       <c r="L3" t="str">
-        <v>SEM LINHAS</v>
+        <v>CONCLUIDO</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>11/05/2026, 22:21:47</v>
+        <v>12/05/2026, 15:25:52</v>
       </c>
       <c r="B4" t="str">
         <v>lmalerbo</v>
       </c>
       <c r="C4">
-        <v>10688003</v>
+        <v>10359001</v>
       </c>
       <c r="D4">
-        <v>10688</v>
+        <v>10359</v>
       </c>
       <c r="E4" t="str">
-        <v>2-M</v>
+        <v>AGUAS BOAS</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>18.51</v>
       </c>
       <c r="J4" t="str">
-        <v>SEM LINHAS</v>
+        <v>VANT</v>
       </c>
       <c r="K4" t="str">
-        <v>25-26</v>
+        <v>26-27</v>
       </c>
       <c r="L4" t="str">
-        <v>SEM LINHAS</v>
+        <v>CONCLUIDO</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>12/05/2026, 09:50:50</v>
+        <v>12/05/2026, 15:25:52</v>
       </c>
       <c r="B5" t="str">
         <v>lmalerbo</v>
       </c>
       <c r="C5">
-        <v>10696001</v>
+        <v>10359002</v>
       </c>
       <c r="D5">
-        <v>10696</v>
+        <v>10359</v>
       </c>
       <c r="E5" t="str">
-        <v>2M 2</v>
+        <v>AGUAS BOAS</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>12.43</v>
+        <v>17.13</v>
       </c>
       <c r="J5" t="str">
         <v>VANT</v>
@@ -605,31 +605,31 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>12/05/2026, 09:50:50</v>
+        <v>12/05/2026, 15:25:52</v>
       </c>
       <c r="B6" t="str">
         <v>lmalerbo</v>
       </c>
       <c r="C6">
-        <v>10696002</v>
+        <v>10359003</v>
       </c>
       <c r="D6">
-        <v>10696</v>
+        <v>10359</v>
       </c>
       <c r="E6" t="str">
-        <v>2M 2</v>
+        <v>AGUAS BOAS</v>
       </c>
       <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
         <v>2</v>
       </c>
-      <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
       <c r="I6">
-        <v>33.87</v>
+        <v>5.8</v>
       </c>
       <c r="J6" t="str">
         <v>VANT</v>
@@ -643,31 +643,31 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>12/05/2026, 09:50:50</v>
+        <v>12/05/2026, 15:25:52</v>
       </c>
       <c r="B7" t="str">
         <v>lmalerbo</v>
       </c>
       <c r="C7">
-        <v>10696003</v>
+        <v>10359004</v>
       </c>
       <c r="D7">
-        <v>10696</v>
+        <v>10359</v>
       </c>
       <c r="E7" t="str">
-        <v>2M 2</v>
+        <v>AGUAS BOAS</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>13.72</v>
+        <v>9.18</v>
       </c>
       <c r="J7" t="str">
         <v>VANT</v>
@@ -681,31 +681,31 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>12/05/2026, 09:50:50</v>
+        <v>12/05/2026, 15:25:52</v>
       </c>
       <c r="B8" t="str">
         <v>lmalerbo</v>
       </c>
       <c r="C8">
-        <v>10696004</v>
+        <v>10359005</v>
       </c>
       <c r="D8">
-        <v>10696</v>
+        <v>10359</v>
       </c>
       <c r="E8" t="str">
-        <v>2M 2</v>
+        <v>AGUAS BOAS</v>
       </c>
       <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
         <v>4</v>
       </c>
-      <c r="G8">
-        <v>9</v>
-      </c>
       <c r="H8">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I8">
-        <v>18.62</v>
+        <v>16.85</v>
       </c>
       <c r="J8" t="str">
         <v>VANT</v>
@@ -719,31 +719,31 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>12/05/2026, 09:50:50</v>
+        <v>12/05/2026, 15:25:52</v>
       </c>
       <c r="B9" t="str">
         <v>lmalerbo</v>
       </c>
       <c r="C9">
-        <v>10696005</v>
+        <v>10359006</v>
       </c>
       <c r="D9">
-        <v>10696</v>
+        <v>10359</v>
       </c>
       <c r="E9" t="str">
-        <v>2M 2</v>
+        <v>AGUAS BOAS</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H9">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="I9">
-        <v>13.72</v>
+        <v>6.23</v>
       </c>
       <c r="J9" t="str">
         <v>VANT</v>
@@ -757,45 +757,235 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>12/05/2026, 09:50:50</v>
+        <v>12/05/2026, 15:29:09</v>
       </c>
       <c r="B10" t="str">
         <v>lmalerbo</v>
       </c>
       <c r="C10">
-        <v>10696006</v>
+        <v>10190002</v>
       </c>
       <c r="D10">
-        <v>10696</v>
+        <v>10190</v>
       </c>
       <c r="E10" t="str">
-        <v>2M 2</v>
+        <v>BARRINHA</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G10">
+        <v>10</v>
+      </c>
+      <c r="H10">
         <v>5</v>
       </c>
-      <c r="H10">
-        <v>27</v>
-      </c>
       <c r="I10">
-        <v>9.4</v>
+        <v>27.38</v>
       </c>
       <c r="J10" t="str">
+        <v>VANT</v>
+      </c>
+      <c r="K10" t="str">
+        <v>26-27</v>
+      </c>
+      <c r="L10" t="str">
+        <v>CONCLUIDO</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>12/05/2026, 15:35:01</v>
+      </c>
+      <c r="B11" t="str">
+        <v>lmalerbo</v>
+      </c>
+      <c r="C11">
+        <v>10650002</v>
+      </c>
+      <c r="D11">
+        <v>10650</v>
+      </c>
+      <c r="E11" t="str">
+        <v>COQUEIRAL</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" t="str">
+        <v>—</v>
+      </c>
+      <c r="H11" t="str">
+        <v>—</v>
+      </c>
+      <c r="I11">
+        <v>0.55</v>
+      </c>
+      <c r="J11" t="str">
         <v>PROJETO</v>
       </c>
-      <c r="K10" t="str">
-        <v>26-27</v>
-      </c>
-      <c r="L10" t="str">
+      <c r="K11" t="str">
+        <v>26-27</v>
+      </c>
+      <c r="L11" t="str">
+        <v>CONCLUIDO</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>12/05/2026, 15:35:01</v>
+      </c>
+      <c r="B12" t="str">
+        <v>lmalerbo</v>
+      </c>
+      <c r="C12">
+        <v>10650003</v>
+      </c>
+      <c r="D12">
+        <v>10650</v>
+      </c>
+      <c r="E12" t="str">
+        <v>COQUEIRAL</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12" t="str">
+        <v>—</v>
+      </c>
+      <c r="H12" t="str">
+        <v>—</v>
+      </c>
+      <c r="I12">
+        <v>3.32</v>
+      </c>
+      <c r="J12" t="str">
+        <v>PROJETO</v>
+      </c>
+      <c r="K12" t="str">
+        <v>26-27</v>
+      </c>
+      <c r="L12" t="str">
+        <v>CONCLUIDO</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>12/05/2026, 15:35:11</v>
+      </c>
+      <c r="B13" t="str">
+        <v>lmalerbo</v>
+      </c>
+      <c r="C13">
+        <v>10650001</v>
+      </c>
+      <c r="D13">
+        <v>10650</v>
+      </c>
+      <c r="E13" t="str">
+        <v>COQUEIRAL</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="str">
+        <v>—</v>
+      </c>
+      <c r="H13" t="str">
+        <v>—</v>
+      </c>
+      <c r="I13">
+        <v>21.06</v>
+      </c>
+      <c r="J13" t="str">
+        <v>VANT</v>
+      </c>
+      <c r="K13" t="str">
+        <v>26-27</v>
+      </c>
+      <c r="L13" t="str">
+        <v>CONCLUIDO</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>12/05/2026, 15:35:11</v>
+      </c>
+      <c r="B14" t="str">
+        <v>lmalerbo</v>
+      </c>
+      <c r="C14">
+        <v>10650004</v>
+      </c>
+      <c r="D14">
+        <v>10650</v>
+      </c>
+      <c r="E14" t="str">
+        <v>COQUEIRAL</v>
+      </c>
+      <c r="F14">
+        <v>4</v>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
+      <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14">
+        <v>9.65</v>
+      </c>
+      <c r="J14" t="str">
+        <v>VANT</v>
+      </c>
+      <c r="K14" t="str">
+        <v>26-27</v>
+      </c>
+      <c r="L14" t="str">
+        <v>CONCLUIDO</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>12/05/2026, 15:35:11</v>
+      </c>
+      <c r="B15" t="str">
+        <v>lmalerbo</v>
+      </c>
+      <c r="C15">
+        <v>10650005</v>
+      </c>
+      <c r="D15">
+        <v>10650</v>
+      </c>
+      <c r="E15" t="str">
+        <v>COQUEIRAL</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+      <c r="G15" t="str">
+        <v>—</v>
+      </c>
+      <c r="H15" t="str">
+        <v>—</v>
+      </c>
+      <c r="I15">
+        <v>13.84</v>
+      </c>
+      <c r="J15" t="str">
+        <v>VANT</v>
+      </c>
+      <c r="K15" t="str">
+        <v>26-27</v>
+      </c>
+      <c r="L15" t="str">
         <v>CONCLUIDO</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
   </ignoredErrors>
 </worksheet>
 </file>